--- a/construction_cost_predictor/outputs/04_model_results.xlsx
+++ b/construction_cost_predictor/outputs/04_model_results.xlsx
@@ -456,27 +456,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5.68% [4.71%, 6.69%]</t>
+          <t>6.76% [5.30%, 8.22%]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>340</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>264</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.8852</t>
+          <t>0.8627</t>
         </is>
       </c>
     </row>
@@ -488,27 +488,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12.17</t>
+          <t>14.11</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12.17% [9.71%, 14.53%]</t>
+          <t>14.12% [10.77%, 17.63%]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>785</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>557</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.3161</t>
+          <t>0.2671</t>
         </is>
       </c>
     </row>
@@ -520,27 +520,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8.91</t>
+          <t>9.30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8.88% [7.01%, 10.69%]</t>
+          <t>9.33% [6.55%, 12.37%]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>627</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>387</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.5759</t>
+          <t>0.5334</t>
         </is>
       </c>
     </row>
@@ -552,27 +552,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9.99% [7.89%, 11.92%]</t>
+          <t>9.70% [6.77%, 12.83%]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>653</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>397</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.4879</t>
+          <t>0.4929</t>
         </is>
       </c>
     </row>
@@ -584,27 +584,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>9.36</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9.03% [7.05%, 10.92%]</t>
+          <t>9.39% [6.47%, 12.62%]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>646</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>389</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.5489</t>
+          <t>0.5041</t>
         </is>
       </c>
     </row>
